--- a/data/trans_orig/IP1018-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134934</t>
+          <t>134424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150128</t>
+          <t>150842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286876</t>
+          <t>287351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191904</t>
+          <t>191901</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209048</t>
+          <t>208177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402654</t>
+          <t>402633</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>145339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283272</t>
+          <t>283525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676287</t>
+          <t>676184</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717242</t>
+          <t>717804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396479</t>
+          <t>1396145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402480</t>
+          <t>1402521</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142663</t>
+          <t>141744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276319</t>
+          <t>276179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>204007</t>
+          <t>203925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428189</t>
+          <t>428593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163351</t>
+          <t>163210</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319713</t>
+          <t>319725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202590</t>
+          <t>203132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408797</t>
+          <t>408820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>698947</t>
+          <t>698850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>703789</t>
+          <t>703788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739343</t>
+          <t>739256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1441262</t>
+          <t>1440989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448037</t>
+          <t>1448022</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1018-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1018-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2922</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4302</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3601</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2235</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4452</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152552</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>150155</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138006</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>134424</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>135125</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152552</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>150842</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>427</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287351</t>
+          <t>287140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,87 +1070,87 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3965</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211463</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208751</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194509</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191901</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191862</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>211463</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>208177</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>632</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402633</t>
+          <t>402628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4116</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>719</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4318</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3949</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148938</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>145541</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148938</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>145339</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283525</t>
+          <t>283401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1374</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4837</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4869</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4896</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720777</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>716943</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722175</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,93%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679647</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676184</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676152</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720777</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>717804</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722177</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396145</t>
+          <t>1396244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402521</t>
+          <t>1403000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3811,47 +3811,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4154,47 +4154,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5457</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1088</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6332</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5604</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>146988</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>142619</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>146988</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141744</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276179</t>
+          <t>276344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3322</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3013</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>206643</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>203925</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>203701</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>665</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428593</t>
+          <t>428518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2981</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3463</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3543</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2945</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166085</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>163692</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166085</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>163210</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319725</t>
+          <t>319127</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1221</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4579</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4336</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>206199</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>203132</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>203215</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>569</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408820</t>
+          <t>408577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6377</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1824</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5521</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5523</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5588</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>743168</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738467</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>702547</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698850</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>703788</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698848</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>703789</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>743168</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739256</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2121</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1440989</t>
+          <t>1441344</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448022</t>
+          <t>1447991</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
